--- a/Catalogo_completo_reglas_chatbot_valeras.xlsx
+++ b/Catalogo_completo_reglas_chatbot_valeras.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reglas Chatbot" sheetId="1" r:id="R6888a443311b4bb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo Métricas" sheetId="2" r:id="Re580177315b54345"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diccionario Columnas" sheetId="3" r:id="Rcf3c4fdd3e8e4236"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categorías Bonificaciones" sheetId="4" r:id="R339ce79dcac14971"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preguntas Ejemplo" sheetId="5" r:id="Rf9148b584c0e49c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sintaxis Fórmulas" sheetId="6" r:id="R2ae6dcda45ab4095"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guía Implementación" sheetId="7" r:id="Rb2d91f50a1eb48ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reglas Chatbot" sheetId="1" r:id="R3337a7c4fd514ad8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo Métricas" sheetId="2" r:id="R7c4be78051fc40d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diccionario Columnas" sheetId="3" r:id="R8f238c45d870462a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categorías Bonificaciones" sheetId="4" r:id="Rb082cec98b274995"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preguntas Ejemplo" sheetId="5" r:id="R214cd387f5bf458f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sintaxis Fórmulas" sheetId="6" r:id="R90e8b8e8aa8e42df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guía Implementación" sheetId="7" r:id="R7ba6a85595924309"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz Comparaciones" sheetId="8" r:id="R570f57a0685947c1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -48,7 +49,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -80,99 +81,62 @@
         <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="24">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="119">
+  <x:cellXfs count="133">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -505,6 +469,38 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -516,7 +512,7 @@
         <x:color rgb="FF274E13"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
@@ -526,7 +522,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -536,7 +532,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReglasChatbotTable" displayName="ReglasChatbotTable" ref="A3:L91" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReglasChatbotTable" displayName="ReglasChatbotTable" ref="A3:L118" headerRowCount="1">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="Intención"/>
     <x:tableColumn id="2" name="Palabras clave"/>
@@ -585,7 +581,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PreguntasTable" displayName="PreguntasTable" ref="A3:E91" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PreguntasTable" displayName="PreguntasTable" ref="A3:E118" headerRowCount="1">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Intención"/>
     <x:tableColumn id="2" name="Pregunta ejemplo"/>
@@ -606,6 +602,22 @@
     <x:tableColumn id="4" name="Ejemplo"/>
     <x:tableColumn id="5" name="Regla de ejecución"/>
     <x:tableColumn id="6" name="Advertencia"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="MatrizComparacionesTable" displayName="MatrizComparacionesTable" ref="A3:H23" headerRowCount="1">
+  <x:tableColumns count="8">
+    <x:tableColumn id="1" name="Nivel estructural"/>
+    <x:tableColumn id="2" name="Variable"/>
+    <x:tableColumn id="3" name="Base origen"/>
+    <x:tableColumn id="4" name="Campo(s)"/>
+    <x:tableColumn id="5" name="Cálculo"/>
+    <x:tableColumn id="6" name="Orden recomendado"/>
+    <x:tableColumn id="7" name="Pregunta ejemplo"/>
+    <x:tableColumn id="8" name="Respuesta esperada"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </x:table>
@@ -4172,6 +4184,1032 @@
         <x:v>Respuesta fija basada en conocimiento del negocio.</x:v>
       </x:c>
     </x:row>
+    <x:row r="92" ht="62" customHeight="1">
+      <x:c r="A92" s="123" t="str">
+        <x:v>comparar_estructura_completa</x:v>
+      </x:c>
+      <x:c r="B92" s="28" t="str">
+        <x:v>compara toda la estructura, comparación completa, comparar subdirecciones zonas sucursales coordinaciones, panorama comparativo</x:v>
+      </x:c>
+      <x:c r="C92" s="28" t="str">
+        <x:v>Distribuidoras MX + Dispersión diaria + Plazo y composición</x:v>
+      </x:c>
+      <x:c r="D92" s="28" t="str">
+        <x:v>Canjes; Total dispersado; Interes; Capital; Distribuidoras al Corriente H; Distribuidoras en Mora H</x:v>
+      </x:c>
+      <x:c r="E92" s="124" t="str">
+        <x:v>COMPARE_ALL_LEVELS([Subdirección,Zona,Sucursal,Coordinacion],[Canjes,Total dispersado,Tasa de ganancia,Distribuidoras al Corriente H,Distribuidoras en Mora H])</x:v>
+      </x:c>
+      <x:c r="F92" s="28" t="str">
+        <x:v>Toda la estructura</x:v>
+      </x:c>
+      <x:c r="G92" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros activos; excluir Sin dato; usar último corte válido por base</x:v>
+      </x:c>
+      <x:c r="H92" s="28" t="str">
+        <x:v>DESC por variable seleccionada</x:v>
+      </x:c>
+      <x:c r="I92" s="28" t="str">
+        <x:v>Tabla comparativa mixta</x:v>
+      </x:c>
+      <x:c r="J92" s="125" t="str">
+        <x:v>La comparación integral de la estructura identifica líderes y rezagos en canjes, dispersión, tasa de ganancia, distribuidoras al corriente y distribuidoras con mora para cada nivel organizacional.</x:v>
+      </x:c>
+      <x:c r="K92" s="28" t="str">
+        <x:v>Compara toda la estructura con canjes, dispersión, tasa de ganancia, distribuidoras al corriente y con mora</x:v>
+      </x:c>
+      <x:c r="L92" s="28" t="str">
+        <x:v>Debe generar una tabla por Subdirección, Zona, Sucursal y Coordinación. La tasa se calcula ponderada: SUM(Interes)/SUM(Capital).</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="62" customHeight="1">
+      <x:c r="A93" s="123" t="str">
+        <x:v>comparar_canjes_estructura</x:v>
+      </x:c>
+      <x:c r="B93" s="28" t="str">
+        <x:v>compara canjes, comparación de canjes, canjes por estructura, ranking de canjes, compara entre toda la estructura</x:v>
+      </x:c>
+      <x:c r="C93" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D93" s="28" t="str">
+        <x:v>Canjes</x:v>
+      </x:c>
+      <x:c r="E93" s="124" t="str">
+        <x:v>SUM(Canjes)</x:v>
+      </x:c>
+      <x:c r="F93" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+      <x:c r="G93" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H93" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I93" s="28" t="str">
+        <x:v>Número</x:v>
+      </x:c>
+      <x:c r="J93" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} registra {Valor1} canjes y {Entidad2} registra {Valor2}. La diferencia es {Diferencia} canjes y {Lider} presenta el mayor volumen.</x:v>
+      </x:c>
+      <x:c r="K93" s="28" t="str">
+        <x:v>Compara canjes entre toda la estructura</x:v>
+      </x:c>
+      <x:c r="L93" s="28" t="str">
+        <x:v>La pregunta puede indicar dos entidades, un nivel específico o solicitar ranking completo. Debe usar exactamente el mismo corte para todas las entidades.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="62" customHeight="1">
+      <x:c r="A94" s="123" t="str">
+        <x:v>comparar_canjes_subdireccion</x:v>
+      </x:c>
+      <x:c r="B94" s="28" t="str">
+        <x:v>compara canjes por subdirección, comparación de canjes entre subdireccións, ranking de canjes por subdirección</x:v>
+      </x:c>
+      <x:c r="C94" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D94" s="28" t="str">
+        <x:v>Subdirección; Canjes</x:v>
+      </x:c>
+      <x:c r="E94" s="124" t="str">
+        <x:v>SUM(Canjes)</x:v>
+      </x:c>
+      <x:c r="F94" s="28" t="str">
+        <x:v>Subdirección</x:v>
+      </x:c>
+      <x:c r="G94" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H94" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I94" s="28" t="str">
+        <x:v>Número</x:v>
+      </x:c>
+      <x:c r="J94" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} registra {Valor1} canjes y {Entidad2} registra {Valor2}. La diferencia es {Diferencia} canjes y {Lider} presenta el mayor volumen.</x:v>
+      </x:c>
+      <x:c r="K94" s="28" t="str">
+        <x:v>Compara canjes por subdirección</x:v>
+      </x:c>
+      <x:c r="L94" s="28" t="str">
+        <x:v>Permite comparar dos subdireccións o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="62" customHeight="1">
+      <x:c r="A95" s="123" t="str">
+        <x:v>comparar_canjes_zona</x:v>
+      </x:c>
+      <x:c r="B95" s="28" t="str">
+        <x:v>compara canjes por zona, comparación de canjes entre zonas, ranking de canjes por zona</x:v>
+      </x:c>
+      <x:c r="C95" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D95" s="28" t="str">
+        <x:v>Zona; Canjes</x:v>
+      </x:c>
+      <x:c r="E95" s="124" t="str">
+        <x:v>SUM(Canjes)</x:v>
+      </x:c>
+      <x:c r="F95" s="28" t="str">
+        <x:v>Zona</x:v>
+      </x:c>
+      <x:c r="G95" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H95" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I95" s="28" t="str">
+        <x:v>Número</x:v>
+      </x:c>
+      <x:c r="J95" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} registra {Valor1} canjes y {Entidad2} registra {Valor2}. La diferencia es {Diferencia} canjes y {Lider} presenta el mayor volumen.</x:v>
+      </x:c>
+      <x:c r="K95" s="28" t="str">
+        <x:v>Compara canjes por zona</x:v>
+      </x:c>
+      <x:c r="L95" s="28" t="str">
+        <x:v>Permite comparar dos zonas o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="62" customHeight="1">
+      <x:c r="A96" s="123" t="str">
+        <x:v>comparar_canjes_sucursal</x:v>
+      </x:c>
+      <x:c r="B96" s="28" t="str">
+        <x:v>compara canjes por sucursal, comparación de canjes entre sucursals, ranking de canjes por sucursal</x:v>
+      </x:c>
+      <x:c r="C96" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D96" s="28" t="str">
+        <x:v>Sucursal; Canjes</x:v>
+      </x:c>
+      <x:c r="E96" s="124" t="str">
+        <x:v>SUM(Canjes)</x:v>
+      </x:c>
+      <x:c r="F96" s="28" t="str">
+        <x:v>Sucursal</x:v>
+      </x:c>
+      <x:c r="G96" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H96" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I96" s="28" t="str">
+        <x:v>Número</x:v>
+      </x:c>
+      <x:c r="J96" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} registra {Valor1} canjes y {Entidad2} registra {Valor2}. La diferencia es {Diferencia} canjes y {Lider} presenta el mayor volumen.</x:v>
+      </x:c>
+      <x:c r="K96" s="28" t="str">
+        <x:v>Compara canjes por sucursal</x:v>
+      </x:c>
+      <x:c r="L96" s="28" t="str">
+        <x:v>Permite comparar dos sucursals o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="62" customHeight="1">
+      <x:c r="A97" s="123" t="str">
+        <x:v>comparar_canjes_coordinacion</x:v>
+      </x:c>
+      <x:c r="B97" s="28" t="str">
+        <x:v>compara canjes por coordinación, comparación de canjes entre coordinacións, ranking de canjes por coordinación</x:v>
+      </x:c>
+      <x:c r="C97" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D97" s="28" t="str">
+        <x:v>Coordinacion; Canjes</x:v>
+      </x:c>
+      <x:c r="E97" s="124" t="str">
+        <x:v>SUM(Canjes)</x:v>
+      </x:c>
+      <x:c r="F97" s="28" t="str">
+        <x:v>Coordinacion</x:v>
+      </x:c>
+      <x:c r="G97" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H97" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I97" s="28" t="str">
+        <x:v>Número</x:v>
+      </x:c>
+      <x:c r="J97" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} registra {Valor1} canjes y {Entidad2} registra {Valor2}. La diferencia es {Diferencia} canjes y {Lider} presenta el mayor volumen.</x:v>
+      </x:c>
+      <x:c r="K97" s="28" t="str">
+        <x:v>Compara canjes por coordinación</x:v>
+      </x:c>
+      <x:c r="L97" s="28" t="str">
+        <x:v>Permite comparar dos coordinacións o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="62" customHeight="1">
+      <x:c r="A98" s="123" t="str">
+        <x:v>comparar_dispersion_estructura</x:v>
+      </x:c>
+      <x:c r="B98" s="28" t="str">
+        <x:v>compara dispersión, comparación de dispersado, dispersión por estructura, ranking de dispersión, compara entre toda la estructura</x:v>
+      </x:c>
+      <x:c r="C98" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D98" s="28" t="str">
+        <x:v>Total dispersado</x:v>
+      </x:c>
+      <x:c r="E98" s="124" t="str">
+        <x:v>SUM(Total dispersado)</x:v>
+      </x:c>
+      <x:c r="F98" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+      <x:c r="G98" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H98" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I98" s="28" t="str">
+        <x:v>Moneda</x:v>
+      </x:c>
+      <x:c r="J98" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} acumula {Valor1} de dispersión y {Entidad2} acumula {Valor2}. La diferencia es {Diferencia}; {Lider} concentra el mayor monto.</x:v>
+      </x:c>
+      <x:c r="K98" s="28" t="str">
+        <x:v>Compara dispersión acumulada entre toda la estructura</x:v>
+      </x:c>
+      <x:c r="L98" s="28" t="str">
+        <x:v>La pregunta puede indicar dos entidades, un nivel específico o solicitar ranking completo. Debe usar exactamente el mismo corte para todas las entidades.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="62" customHeight="1">
+      <x:c r="A99" s="123" t="str">
+        <x:v>comparar_dispersion_subdireccion</x:v>
+      </x:c>
+      <x:c r="B99" s="28" t="str">
+        <x:v>compara dispersión acumulada por subdirección, comparación de dispersión acumulada entre subdireccións, ranking de dispersión acumulada por subdirección</x:v>
+      </x:c>
+      <x:c r="C99" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D99" s="28" t="str">
+        <x:v>Subdirección; Total dispersado</x:v>
+      </x:c>
+      <x:c r="E99" s="124" t="str">
+        <x:v>SUM(Total dispersado)</x:v>
+      </x:c>
+      <x:c r="F99" s="28" t="str">
+        <x:v>Subdirección</x:v>
+      </x:c>
+      <x:c r="G99" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H99" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I99" s="28" t="str">
+        <x:v>Moneda</x:v>
+      </x:c>
+      <x:c r="J99" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} acumula {Valor1} de dispersión y {Entidad2} acumula {Valor2}. La diferencia es {Diferencia}; {Lider} concentra el mayor monto.</x:v>
+      </x:c>
+      <x:c r="K99" s="28" t="str">
+        <x:v>Compara dispersión acumulada por subdirección</x:v>
+      </x:c>
+      <x:c r="L99" s="28" t="str">
+        <x:v>Permite comparar dos subdireccións o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="62" customHeight="1">
+      <x:c r="A100" s="123" t="str">
+        <x:v>comparar_dispersion_zona</x:v>
+      </x:c>
+      <x:c r="B100" s="28" t="str">
+        <x:v>compara dispersión acumulada por zona, comparación de dispersión acumulada entre zonas, ranking de dispersión acumulada por zona</x:v>
+      </x:c>
+      <x:c r="C100" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D100" s="28" t="str">
+        <x:v>Zona; Total dispersado</x:v>
+      </x:c>
+      <x:c r="E100" s="124" t="str">
+        <x:v>SUM(Total dispersado)</x:v>
+      </x:c>
+      <x:c r="F100" s="28" t="str">
+        <x:v>Zona</x:v>
+      </x:c>
+      <x:c r="G100" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H100" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I100" s="28" t="str">
+        <x:v>Moneda</x:v>
+      </x:c>
+      <x:c r="J100" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} acumula {Valor1} de dispersión y {Entidad2} acumula {Valor2}. La diferencia es {Diferencia}; {Lider} concentra el mayor monto.</x:v>
+      </x:c>
+      <x:c r="K100" s="28" t="str">
+        <x:v>Compara dispersión acumulada por zona</x:v>
+      </x:c>
+      <x:c r="L100" s="28" t="str">
+        <x:v>Permite comparar dos zonas o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="62" customHeight="1">
+      <x:c r="A101" s="123" t="str">
+        <x:v>comparar_dispersion_sucursal</x:v>
+      </x:c>
+      <x:c r="B101" s="28" t="str">
+        <x:v>compara dispersión acumulada por sucursal, comparación de dispersión acumulada entre sucursals, ranking de dispersión acumulada por sucursal</x:v>
+      </x:c>
+      <x:c r="C101" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D101" s="28" t="str">
+        <x:v>Sucursal; Total dispersado</x:v>
+      </x:c>
+      <x:c r="E101" s="124" t="str">
+        <x:v>SUM(Total dispersado)</x:v>
+      </x:c>
+      <x:c r="F101" s="28" t="str">
+        <x:v>Sucursal</x:v>
+      </x:c>
+      <x:c r="G101" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H101" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I101" s="28" t="str">
+        <x:v>Moneda</x:v>
+      </x:c>
+      <x:c r="J101" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} acumula {Valor1} de dispersión y {Entidad2} acumula {Valor2}. La diferencia es {Diferencia}; {Lider} concentra el mayor monto.</x:v>
+      </x:c>
+      <x:c r="K101" s="28" t="str">
+        <x:v>Compara dispersión acumulada por sucursal</x:v>
+      </x:c>
+      <x:c r="L101" s="28" t="str">
+        <x:v>Permite comparar dos sucursals o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="62" customHeight="1">
+      <x:c r="A102" s="123" t="str">
+        <x:v>comparar_dispersion_coordinacion</x:v>
+      </x:c>
+      <x:c r="B102" s="28" t="str">
+        <x:v>compara dispersión acumulada por coordinación, comparación de dispersión acumulada entre coordinacións, ranking de dispersión acumulada por coordinación</x:v>
+      </x:c>
+      <x:c r="C102" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D102" s="28" t="str">
+        <x:v>Coordinacion; Total dispersado</x:v>
+      </x:c>
+      <x:c r="E102" s="124" t="str">
+        <x:v>SUM(Total dispersado)</x:v>
+      </x:c>
+      <x:c r="F102" s="28" t="str">
+        <x:v>Coordinacion</x:v>
+      </x:c>
+      <x:c r="G102" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H102" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I102" s="28" t="str">
+        <x:v>Moneda</x:v>
+      </x:c>
+      <x:c r="J102" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} acumula {Valor1} de dispersión y {Entidad2} acumula {Valor2}. La diferencia es {Diferencia}; {Lider} concentra el mayor monto.</x:v>
+      </x:c>
+      <x:c r="K102" s="28" t="str">
+        <x:v>Compara dispersión acumulada por coordinación</x:v>
+      </x:c>
+      <x:c r="L102" s="28" t="str">
+        <x:v>Permite comparar dos coordinacións o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="62" customHeight="1">
+      <x:c r="A103" s="123" t="str">
+        <x:v>comparar_tasa_ganancia_estructura</x:v>
+      </x:c>
+      <x:c r="B103" s="28" t="str">
+        <x:v>compara tasa de ganancia, comparación de rentabilidad, tasa por estructura, ranking de tasa, compara entre toda la estructura</x:v>
+      </x:c>
+      <x:c r="C103" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="D103" s="28" t="str">
+        <x:v>Interes; Capital</x:v>
+      </x:c>
+      <x:c r="E103" s="124" t="str">
+        <x:v>DIV(SUM(Interes),SUM(Capital))*100</x:v>
+      </x:c>
+      <x:c r="F103" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+      <x:c r="G103" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H103" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I103" s="28" t="str">
+        <x:v>Porcentaje</x:v>
+      </x:c>
+      <x:c r="J103" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} presenta una tasa de ganancia de {Valor1}% y {Entidad2} de {Valor2}%. La diferencia es {Diferencia} puntos porcentuales; {Lider} tiene la mayor rentabilidad esperada.</x:v>
+      </x:c>
+      <x:c r="K103" s="28" t="str">
+        <x:v>Compara tasa de ganancia entre toda la estructura</x:v>
+      </x:c>
+      <x:c r="L103" s="28" t="str">
+        <x:v>La pregunta puede indicar dos entidades, un nivel específico o solicitar ranking completo. Debe usar exactamente el mismo corte para todas las entidades.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="62" customHeight="1">
+      <x:c r="A104" s="123" t="str">
+        <x:v>comparar_tasa_ganancia_subdireccion</x:v>
+      </x:c>
+      <x:c r="B104" s="28" t="str">
+        <x:v>compara tasa de ganancia por subdirección, comparación de tasa de ganancia entre subdireccións, ranking de tasa de ganancia por subdirección</x:v>
+      </x:c>
+      <x:c r="C104" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="D104" s="28" t="str">
+        <x:v>Subdirección; Interes; Capital</x:v>
+      </x:c>
+      <x:c r="E104" s="124" t="str">
+        <x:v>DIV(SUM(Interes),SUM(Capital))*100</x:v>
+      </x:c>
+      <x:c r="F104" s="28" t="str">
+        <x:v>Subdirección</x:v>
+      </x:c>
+      <x:c r="G104" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H104" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I104" s="28" t="str">
+        <x:v>Porcentaje</x:v>
+      </x:c>
+      <x:c r="J104" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} presenta una tasa de ganancia de {Valor1}% y {Entidad2} de {Valor2}%. La diferencia es {Diferencia} puntos porcentuales; {Lider} tiene la mayor rentabilidad esperada.</x:v>
+      </x:c>
+      <x:c r="K104" s="28" t="str">
+        <x:v>Compara tasa de ganancia por subdirección</x:v>
+      </x:c>
+      <x:c r="L104" s="28" t="str">
+        <x:v>Permite comparar dos subdireccións o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="62" customHeight="1">
+      <x:c r="A105" s="123" t="str">
+        <x:v>comparar_tasa_ganancia_zona</x:v>
+      </x:c>
+      <x:c r="B105" s="28" t="str">
+        <x:v>compara tasa de ganancia por zona, comparación de tasa de ganancia entre zonas, ranking de tasa de ganancia por zona</x:v>
+      </x:c>
+      <x:c r="C105" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="D105" s="28" t="str">
+        <x:v>Zona; Interes; Capital</x:v>
+      </x:c>
+      <x:c r="E105" s="124" t="str">
+        <x:v>DIV(SUM(Interes),SUM(Capital))*100</x:v>
+      </x:c>
+      <x:c r="F105" s="28" t="str">
+        <x:v>Zona</x:v>
+      </x:c>
+      <x:c r="G105" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H105" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I105" s="28" t="str">
+        <x:v>Porcentaje</x:v>
+      </x:c>
+      <x:c r="J105" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} presenta una tasa de ganancia de {Valor1}% y {Entidad2} de {Valor2}%. La diferencia es {Diferencia} puntos porcentuales; {Lider} tiene la mayor rentabilidad esperada.</x:v>
+      </x:c>
+      <x:c r="K105" s="28" t="str">
+        <x:v>Compara tasa de ganancia por zona</x:v>
+      </x:c>
+      <x:c r="L105" s="28" t="str">
+        <x:v>Permite comparar dos zonas o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="62" customHeight="1">
+      <x:c r="A106" s="123" t="str">
+        <x:v>comparar_tasa_ganancia_sucursal</x:v>
+      </x:c>
+      <x:c r="B106" s="28" t="str">
+        <x:v>compara tasa de ganancia por sucursal, comparación de tasa de ganancia entre sucursals, ranking de tasa de ganancia por sucursal</x:v>
+      </x:c>
+      <x:c r="C106" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="D106" s="28" t="str">
+        <x:v>Sucursal; Interes; Capital</x:v>
+      </x:c>
+      <x:c r="E106" s="124" t="str">
+        <x:v>DIV(SUM(Interes),SUM(Capital))*100</x:v>
+      </x:c>
+      <x:c r="F106" s="28" t="str">
+        <x:v>Sucursal</x:v>
+      </x:c>
+      <x:c r="G106" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H106" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I106" s="28" t="str">
+        <x:v>Porcentaje</x:v>
+      </x:c>
+      <x:c r="J106" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} presenta una tasa de ganancia de {Valor1}% y {Entidad2} de {Valor2}%. La diferencia es {Diferencia} puntos porcentuales; {Lider} tiene la mayor rentabilidad esperada.</x:v>
+      </x:c>
+      <x:c r="K106" s="28" t="str">
+        <x:v>Compara tasa de ganancia por sucursal</x:v>
+      </x:c>
+      <x:c r="L106" s="28" t="str">
+        <x:v>Permite comparar dos sucursals o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="62" customHeight="1">
+      <x:c r="A107" s="123" t="str">
+        <x:v>comparar_tasa_ganancia_coordinacion</x:v>
+      </x:c>
+      <x:c r="B107" s="28" t="str">
+        <x:v>compara tasa de ganancia por coordinación, comparación de tasa de ganancia entre coordinacións, ranking de tasa de ganancia por coordinación</x:v>
+      </x:c>
+      <x:c r="C107" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="D107" s="28" t="str">
+        <x:v>Coordinacion; Interes; Capital</x:v>
+      </x:c>
+      <x:c r="E107" s="124" t="str">
+        <x:v>DIV(SUM(Interes),SUM(Capital))*100</x:v>
+      </x:c>
+      <x:c r="F107" s="28" t="str">
+        <x:v>Coordinacion</x:v>
+      </x:c>
+      <x:c r="G107" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H107" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I107" s="28" t="str">
+        <x:v>Porcentaje</x:v>
+      </x:c>
+      <x:c r="J107" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} presenta una tasa de ganancia de {Valor1}% y {Entidad2} de {Valor2}%. La diferencia es {Diferencia} puntos porcentuales; {Lider} tiene la mayor rentabilidad esperada.</x:v>
+      </x:c>
+      <x:c r="K107" s="28" t="str">
+        <x:v>Compara tasa de ganancia por coordinación</x:v>
+      </x:c>
+      <x:c r="L107" s="28" t="str">
+        <x:v>Permite comparar dos coordinacións o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="62" customHeight="1">
+      <x:c r="A108" s="123" t="str">
+        <x:v>comparar_distribuidoras_corriente_estructura</x:v>
+      </x:c>
+      <x:c r="B108" s="28" t="str">
+        <x:v>compara distribuidoras al corriente, comparación al corriente, corriente por estructura, ranking al corriente, compara entre toda la estructura</x:v>
+      </x:c>
+      <x:c r="C108" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D108" s="28" t="str">
+        <x:v>Distribuidoras al Corriente H</x:v>
+      </x:c>
+      <x:c r="E108" s="124" t="str">
+        <x:v>SUM(Distribuidoras al Corriente H)</x:v>
+      </x:c>
+      <x:c r="F108" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+      <x:c r="G108" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H108" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I108" s="28" t="str">
+        <x:v>Número</x:v>
+      </x:c>
+      <x:c r="J108" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras al corriente y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor base al corriente.</x:v>
+      </x:c>
+      <x:c r="K108" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente entre toda la estructura</x:v>
+      </x:c>
+      <x:c r="L108" s="28" t="str">
+        <x:v>La pregunta puede indicar dos entidades, un nivel específico o solicitar ranking completo. Debe usar exactamente el mismo corte para todas las entidades.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="62" customHeight="1">
+      <x:c r="A109" s="123" t="str">
+        <x:v>comparar_distribuidoras_corriente_subdireccion</x:v>
+      </x:c>
+      <x:c r="B109" s="28" t="str">
+        <x:v>compara distribuidoras al corriente por subdirección, comparación de distribuidoras al corriente entre subdireccións, ranking de distribuidoras al corriente por subdirección</x:v>
+      </x:c>
+      <x:c r="C109" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D109" s="28" t="str">
+        <x:v>Subdirección; Distribuidoras al Corriente H</x:v>
+      </x:c>
+      <x:c r="E109" s="124" t="str">
+        <x:v>SUM(Distribuidoras al Corriente H)</x:v>
+      </x:c>
+      <x:c r="F109" s="28" t="str">
+        <x:v>Subdirección</x:v>
+      </x:c>
+      <x:c r="G109" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H109" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I109" s="28" t="str">
+        <x:v>Número</x:v>
+      </x:c>
+      <x:c r="J109" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras al corriente y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor base al corriente.</x:v>
+      </x:c>
+      <x:c r="K109" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente por subdirección</x:v>
+      </x:c>
+      <x:c r="L109" s="28" t="str">
+        <x:v>Permite comparar dos subdireccións o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="62" customHeight="1">
+      <x:c r="A110" s="123" t="str">
+        <x:v>comparar_distribuidoras_corriente_zona</x:v>
+      </x:c>
+      <x:c r="B110" s="28" t="str">
+        <x:v>compara distribuidoras al corriente por zona, comparación de distribuidoras al corriente entre zonas, ranking de distribuidoras al corriente por zona</x:v>
+      </x:c>
+      <x:c r="C110" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D110" s="28" t="str">
+        <x:v>Zona; Distribuidoras al Corriente H</x:v>
+      </x:c>
+      <x:c r="E110" s="124" t="str">
+        <x:v>SUM(Distribuidoras al Corriente H)</x:v>
+      </x:c>
+      <x:c r="F110" s="28" t="str">
+        <x:v>Zona</x:v>
+      </x:c>
+      <x:c r="G110" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H110" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I110" s="28" t="str">
+        <x:v>Número</x:v>
+      </x:c>
+      <x:c r="J110" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras al corriente y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor base al corriente.</x:v>
+      </x:c>
+      <x:c r="K110" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente por zona</x:v>
+      </x:c>
+      <x:c r="L110" s="28" t="str">
+        <x:v>Permite comparar dos zonas o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="62" customHeight="1">
+      <x:c r="A111" s="123" t="str">
+        <x:v>comparar_distribuidoras_corriente_sucursal</x:v>
+      </x:c>
+      <x:c r="B111" s="28" t="str">
+        <x:v>compara distribuidoras al corriente por sucursal, comparación de distribuidoras al corriente entre sucursals, ranking de distribuidoras al corriente por sucursal</x:v>
+      </x:c>
+      <x:c r="C111" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D111" s="28" t="str">
+        <x:v>Sucursal; Distribuidoras al Corriente H</x:v>
+      </x:c>
+      <x:c r="E111" s="124" t="str">
+        <x:v>SUM(Distribuidoras al Corriente H)</x:v>
+      </x:c>
+      <x:c r="F111" s="28" t="str">
+        <x:v>Sucursal</x:v>
+      </x:c>
+      <x:c r="G111" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H111" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I111" s="28" t="str">
+        <x:v>Número</x:v>
+      </x:c>
+      <x:c r="J111" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras al corriente y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor base al corriente.</x:v>
+      </x:c>
+      <x:c r="K111" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente por sucursal</x:v>
+      </x:c>
+      <x:c r="L111" s="28" t="str">
+        <x:v>Permite comparar dos sucursals o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="62" customHeight="1">
+      <x:c r="A112" s="123" t="str">
+        <x:v>comparar_distribuidoras_corriente_coordinacion</x:v>
+      </x:c>
+      <x:c r="B112" s="28" t="str">
+        <x:v>compara distribuidoras al corriente por coordinación, comparación de distribuidoras al corriente entre coordinacións, ranking de distribuidoras al corriente por coordinación</x:v>
+      </x:c>
+      <x:c r="C112" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D112" s="28" t="str">
+        <x:v>Coordinacion; Distribuidoras al Corriente H</x:v>
+      </x:c>
+      <x:c r="E112" s="124" t="str">
+        <x:v>SUM(Distribuidoras al Corriente H)</x:v>
+      </x:c>
+      <x:c r="F112" s="28" t="str">
+        <x:v>Coordinacion</x:v>
+      </x:c>
+      <x:c r="G112" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H112" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I112" s="28" t="str">
+        <x:v>Número</x:v>
+      </x:c>
+      <x:c r="J112" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras al corriente y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor base al corriente.</x:v>
+      </x:c>
+      <x:c r="K112" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente por coordinación</x:v>
+      </x:c>
+      <x:c r="L112" s="28" t="str">
+        <x:v>Permite comparar dos coordinacións o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="62" customHeight="1">
+      <x:c r="A113" s="123" t="str">
+        <x:v>comparar_distribuidoras_mora_estructura</x:v>
+      </x:c>
+      <x:c r="B113" s="28" t="str">
+        <x:v>compara distribuidoras con mora, comparación de mora, mora por estructura, ranking de distribuidoras en mora, compara entre toda la estructura</x:v>
+      </x:c>
+      <x:c r="C113" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D113" s="28" t="str">
+        <x:v>Distribuidoras en Mora H</x:v>
+      </x:c>
+      <x:c r="E113" s="124" t="str">
+        <x:v>SUM(Distribuidoras en Mora H)</x:v>
+      </x:c>
+      <x:c r="F113" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+      <x:c r="G113" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H113" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I113" s="28" t="str">
+        <x:v>Número</x:v>
+      </x:c>
+      <x:c r="J113" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras con mora y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor exposición en mora.</x:v>
+      </x:c>
+      <x:c r="K113" s="28" t="str">
+        <x:v>Compara distribuidoras con mora entre toda la estructura</x:v>
+      </x:c>
+      <x:c r="L113" s="28" t="str">
+        <x:v>La pregunta puede indicar dos entidades, un nivel específico o solicitar ranking completo. Debe usar exactamente el mismo corte para todas las entidades.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="62" customHeight="1">
+      <x:c r="A114" s="123" t="str">
+        <x:v>comparar_distribuidoras_mora_subdireccion</x:v>
+      </x:c>
+      <x:c r="B114" s="28" t="str">
+        <x:v>compara distribuidoras con mora por subdirección, comparación de distribuidoras con mora entre subdireccións, ranking de distribuidoras con mora por subdirección</x:v>
+      </x:c>
+      <x:c r="C114" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D114" s="28" t="str">
+        <x:v>Subdirección; Distribuidoras en Mora H</x:v>
+      </x:c>
+      <x:c r="E114" s="124" t="str">
+        <x:v>SUM(Distribuidoras en Mora H)</x:v>
+      </x:c>
+      <x:c r="F114" s="28" t="str">
+        <x:v>Subdirección</x:v>
+      </x:c>
+      <x:c r="G114" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H114" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I114" s="28" t="str">
+        <x:v>Número</x:v>
+      </x:c>
+      <x:c r="J114" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras con mora y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor exposición en mora.</x:v>
+      </x:c>
+      <x:c r="K114" s="28" t="str">
+        <x:v>Compara distribuidoras con mora por subdirección</x:v>
+      </x:c>
+      <x:c r="L114" s="28" t="str">
+        <x:v>Permite comparar dos subdireccións o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="62" customHeight="1">
+      <x:c r="A115" s="123" t="str">
+        <x:v>comparar_distribuidoras_mora_zona</x:v>
+      </x:c>
+      <x:c r="B115" s="28" t="str">
+        <x:v>compara distribuidoras con mora por zona, comparación de distribuidoras con mora entre zonas, ranking de distribuidoras con mora por zona</x:v>
+      </x:c>
+      <x:c r="C115" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D115" s="28" t="str">
+        <x:v>Zona; Distribuidoras en Mora H</x:v>
+      </x:c>
+      <x:c r="E115" s="124" t="str">
+        <x:v>SUM(Distribuidoras en Mora H)</x:v>
+      </x:c>
+      <x:c r="F115" s="28" t="str">
+        <x:v>Zona</x:v>
+      </x:c>
+      <x:c r="G115" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H115" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I115" s="28" t="str">
+        <x:v>Número</x:v>
+      </x:c>
+      <x:c r="J115" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras con mora y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor exposición en mora.</x:v>
+      </x:c>
+      <x:c r="K115" s="28" t="str">
+        <x:v>Compara distribuidoras con mora por zona</x:v>
+      </x:c>
+      <x:c r="L115" s="28" t="str">
+        <x:v>Permite comparar dos zonas o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="62" customHeight="1">
+      <x:c r="A116" s="123" t="str">
+        <x:v>comparar_distribuidoras_mora_sucursal</x:v>
+      </x:c>
+      <x:c r="B116" s="28" t="str">
+        <x:v>compara distribuidoras con mora por sucursal, comparación de distribuidoras con mora entre sucursals, ranking de distribuidoras con mora por sucursal</x:v>
+      </x:c>
+      <x:c r="C116" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D116" s="28" t="str">
+        <x:v>Sucursal; Distribuidoras en Mora H</x:v>
+      </x:c>
+      <x:c r="E116" s="124" t="str">
+        <x:v>SUM(Distribuidoras en Mora H)</x:v>
+      </x:c>
+      <x:c r="F116" s="28" t="str">
+        <x:v>Sucursal</x:v>
+      </x:c>
+      <x:c r="G116" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H116" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I116" s="28" t="str">
+        <x:v>Número</x:v>
+      </x:c>
+      <x:c r="J116" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras con mora y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor exposición en mora.</x:v>
+      </x:c>
+      <x:c r="K116" s="28" t="str">
+        <x:v>Compara distribuidoras con mora por sucursal</x:v>
+      </x:c>
+      <x:c r="L116" s="28" t="str">
+        <x:v>Permite comparar dos sucursals o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="62" customHeight="1">
+      <x:c r="A117" s="123" t="str">
+        <x:v>comparar_distribuidoras_mora_coordinacion</x:v>
+      </x:c>
+      <x:c r="B117" s="28" t="str">
+        <x:v>compara distribuidoras con mora por coordinación, comparación de distribuidoras con mora entre coordinacións, ranking de distribuidoras con mora por coordinación</x:v>
+      </x:c>
+      <x:c r="C117" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D117" s="28" t="str">
+        <x:v>Coordinacion; Distribuidoras en Mora H</x:v>
+      </x:c>
+      <x:c r="E117" s="124" t="str">
+        <x:v>SUM(Distribuidoras en Mora H)</x:v>
+      </x:c>
+      <x:c r="F117" s="28" t="str">
+        <x:v>Coordinacion</x:v>
+      </x:c>
+      <x:c r="G117" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros superiores activos; excluir Sin dato; usar último corte válido</x:v>
+      </x:c>
+      <x:c r="H117" s="28" t="str">
+        <x:v>DESC para ranking; comparación directa para dos entidades</x:v>
+      </x:c>
+      <x:c r="I117" s="28" t="str">
+        <x:v>Número</x:v>
+      </x:c>
+      <x:c r="J117" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras con mora y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor exposición en mora.</x:v>
+      </x:c>
+      <x:c r="K117" s="28" t="str">
+        <x:v>Compara distribuidoras con mora por coordinación</x:v>
+      </x:c>
+      <x:c r="L117" s="28" t="str">
+        <x:v>Permite comparar dos coordinacións o devolver un ranking completo. Para tasa de ganancia usar cálculo ponderado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="62" customHeight="1">
+      <x:c r="A118" s="123" t="str">
+        <x:v>comparar_dos_entidades_todas_variables</x:v>
+      </x:c>
+      <x:c r="B118" s="28" t="str">
+        <x:v>compara dos sucursales en todo, compara dos zonas con todas las variables, comparación completa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="C118" s="28" t="str">
+        <x:v>Distribuidoras MX + Dispersión diaria + Plazo y composición</x:v>
+      </x:c>
+      <x:c r="D118" s="28" t="str">
+        <x:v>Canjes; Total dispersado; Interes; Capital; Distribuidoras al Corriente H; Distribuidoras en Mora H</x:v>
+      </x:c>
+      <x:c r="E118" s="124" t="str">
+        <x:v>COMPARE_ENTITIES(entity1,entity2,[Canjes,Total dispersado,DIV(SUM(Interes),SUM(Capital))*100,Distribuidoras al Corriente H,Distribuidoras en Mora H])</x:v>
+      </x:c>
+      <x:c r="F118" s="28" t="str">
+        <x:v>Nivel detectado</x:v>
+      </x:c>
+      <x:c r="G118" s="28" t="str">
+        <x:v>Mismo nivel; marca activa; mismo corte; filtros activos</x:v>
+      </x:c>
+      <x:c r="H118" s="28" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="I118" s="28" t="str">
+        <x:v>Tabla comparativa mixta</x:v>
+      </x:c>
+      <x:c r="J118" s="125" t="str">
+        <x:v>{Entidad1} vs {Entidad2}: canjes {Canjes1} vs {Canjes2}; dispersión {Dispersion1} vs {Dispersion2}; tasa {Tasa1}% vs {Tasa2}%; al corriente {Corriente1} vs {Corriente2}; con mora {Mora1} vs {Mora2}. {Conclusion}.</x:v>
+      </x:c>
+      <x:c r="K118" s="28" t="str">
+        <x:v>Compara Cd. Juárez con Tampico Centro en todas las variables</x:v>
+      </x:c>
+      <x:c r="L118" s="28" t="str">
+        <x:v>La conclusión debe identificar fortalezas y riesgos sin mezclar escalas. La tasa de ganancia es ponderada.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:L1"/>
@@ -4191,7 +5229,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7742b35b6e64e83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf56be3e57d6942b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4985,7 +6023,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3dbb633d92004081"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a3d74b9ffd84475"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6578,7 +7616,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c46c1ccbde34f2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0de2200e373c455b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8650,13 +9688,472 @@
         <x:v>Sin agrupación</x:v>
       </x:c>
     </x:row>
+    <x:row r="92" ht="58" customHeight="1">
+      <x:c r="A92" s="28" t="str">
+        <x:v>comparar_estructura_completa</x:v>
+      </x:c>
+      <x:c r="B92" s="28" t="str">
+        <x:v>Compara toda la estructura con canjes, dispersión, tasa de ganancia, distribuidoras al corriente y con mora</x:v>
+      </x:c>
+      <x:c r="C92" s="28" t="str">
+        <x:v>La comparación integral muestra resultados por Subdirección, Zona, Sucursal y Coordinación para las cinco variables.</x:v>
+      </x:c>
+      <x:c r="D92" s="28" t="str">
+        <x:v>Distribuidoras MX + Dispersión diaria + Plazo y composición</x:v>
+      </x:c>
+      <x:c r="E92" s="28" t="str">
+        <x:v>Toda la estructura</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="58" customHeight="1">
+      <x:c r="A93" s="28" t="str">
+        <x:v>comparar_canjes_estructura</x:v>
+      </x:c>
+      <x:c r="B93" s="28" t="str">
+        <x:v>Compara canjes entre toda la estructura</x:v>
+      </x:c>
+      <x:c r="C93" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} registra {Valor1} canjes y {Entidad2} registra {Valor2}. La diferencia es {Diferencia} canjes y {Lider} presenta el mayor volumen.</x:v>
+      </x:c>
+      <x:c r="D93" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="E93" s="28" t="str">
+        <x:v>Nivel detectado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="58" customHeight="1">
+      <x:c r="A94" s="28" t="str">
+        <x:v>comparar_canjes_subdireccion</x:v>
+      </x:c>
+      <x:c r="B94" s="28" t="str">
+        <x:v>Compara canjes por subdirección</x:v>
+      </x:c>
+      <x:c r="C94" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} registra {Valor1} canjes y {Entidad2} registra {Valor2}. La diferencia es {Diferencia} canjes y {Lider} presenta el mayor volumen.</x:v>
+      </x:c>
+      <x:c r="D94" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="E94" s="28" t="str">
+        <x:v>Subdirección</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="58" customHeight="1">
+      <x:c r="A95" s="28" t="str">
+        <x:v>comparar_canjes_zona</x:v>
+      </x:c>
+      <x:c r="B95" s="28" t="str">
+        <x:v>Compara canjes por zona</x:v>
+      </x:c>
+      <x:c r="C95" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} registra {Valor1} canjes y {Entidad2} registra {Valor2}. La diferencia es {Diferencia} canjes y {Lider} presenta el mayor volumen.</x:v>
+      </x:c>
+      <x:c r="D95" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="E95" s="28" t="str">
+        <x:v>Zona</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="58" customHeight="1">
+      <x:c r="A96" s="28" t="str">
+        <x:v>comparar_canjes_sucursal</x:v>
+      </x:c>
+      <x:c r="B96" s="28" t="str">
+        <x:v>Compara canjes por sucursal</x:v>
+      </x:c>
+      <x:c r="C96" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} registra {Valor1} canjes y {Entidad2} registra {Valor2}. La diferencia es {Diferencia} canjes y {Lider} presenta el mayor volumen.</x:v>
+      </x:c>
+      <x:c r="D96" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="E96" s="28" t="str">
+        <x:v>Sucursal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="58" customHeight="1">
+      <x:c r="A97" s="28" t="str">
+        <x:v>comparar_canjes_coordinacion</x:v>
+      </x:c>
+      <x:c r="B97" s="28" t="str">
+        <x:v>Compara canjes por coordinación</x:v>
+      </x:c>
+      <x:c r="C97" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} registra {Valor1} canjes y {Entidad2} registra {Valor2}. La diferencia es {Diferencia} canjes y {Lider} presenta el mayor volumen.</x:v>
+      </x:c>
+      <x:c r="D97" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="E97" s="28" t="str">
+        <x:v>Coordinacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="58" customHeight="1">
+      <x:c r="A98" s="28" t="str">
+        <x:v>comparar_dispersion_estructura</x:v>
+      </x:c>
+      <x:c r="B98" s="28" t="str">
+        <x:v>Compara dispersión acumulada entre toda la estructura</x:v>
+      </x:c>
+      <x:c r="C98" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} acumula {Valor1} de dispersión y {Entidad2} acumula {Valor2}. La diferencia es {Diferencia}; {Lider} concentra el mayor monto.</x:v>
+      </x:c>
+      <x:c r="D98" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="E98" s="28" t="str">
+        <x:v>Nivel detectado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="58" customHeight="1">
+      <x:c r="A99" s="28" t="str">
+        <x:v>comparar_dispersion_subdireccion</x:v>
+      </x:c>
+      <x:c r="B99" s="28" t="str">
+        <x:v>Compara dispersión acumulada por subdirección</x:v>
+      </x:c>
+      <x:c r="C99" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} acumula {Valor1} de dispersión y {Entidad2} acumula {Valor2}. La diferencia es {Diferencia}; {Lider} concentra el mayor monto.</x:v>
+      </x:c>
+      <x:c r="D99" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="E99" s="28" t="str">
+        <x:v>Subdirección</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="58" customHeight="1">
+      <x:c r="A100" s="28" t="str">
+        <x:v>comparar_dispersion_zona</x:v>
+      </x:c>
+      <x:c r="B100" s="28" t="str">
+        <x:v>Compara dispersión acumulada por zona</x:v>
+      </x:c>
+      <x:c r="C100" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} acumula {Valor1} de dispersión y {Entidad2} acumula {Valor2}. La diferencia es {Diferencia}; {Lider} concentra el mayor monto.</x:v>
+      </x:c>
+      <x:c r="D100" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="E100" s="28" t="str">
+        <x:v>Zona</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="58" customHeight="1">
+      <x:c r="A101" s="28" t="str">
+        <x:v>comparar_dispersion_sucursal</x:v>
+      </x:c>
+      <x:c r="B101" s="28" t="str">
+        <x:v>Compara dispersión acumulada por sucursal</x:v>
+      </x:c>
+      <x:c r="C101" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} acumula {Valor1} de dispersión y {Entidad2} acumula {Valor2}. La diferencia es {Diferencia}; {Lider} concentra el mayor monto.</x:v>
+      </x:c>
+      <x:c r="D101" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="E101" s="28" t="str">
+        <x:v>Sucursal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="58" customHeight="1">
+      <x:c r="A102" s="28" t="str">
+        <x:v>comparar_dispersion_coordinacion</x:v>
+      </x:c>
+      <x:c r="B102" s="28" t="str">
+        <x:v>Compara dispersión acumulada por coordinación</x:v>
+      </x:c>
+      <x:c r="C102" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} acumula {Valor1} de dispersión y {Entidad2} acumula {Valor2}. La diferencia es {Diferencia}; {Lider} concentra el mayor monto.</x:v>
+      </x:c>
+      <x:c r="D102" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="E102" s="28" t="str">
+        <x:v>Coordinacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="58" customHeight="1">
+      <x:c r="A103" s="28" t="str">
+        <x:v>comparar_tasa_ganancia_estructura</x:v>
+      </x:c>
+      <x:c r="B103" s="28" t="str">
+        <x:v>Compara tasa de ganancia entre toda la estructura</x:v>
+      </x:c>
+      <x:c r="C103" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} presenta una tasa de ganancia de {Valor1}% y {Entidad2} de {Valor2}%. La diferencia es {Diferencia} puntos porcentuales; {Lider} tiene la mayor rentabilidad esperada.</x:v>
+      </x:c>
+      <x:c r="D103" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="E103" s="28" t="str">
+        <x:v>Nivel detectado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="58" customHeight="1">
+      <x:c r="A104" s="28" t="str">
+        <x:v>comparar_tasa_ganancia_subdireccion</x:v>
+      </x:c>
+      <x:c r="B104" s="28" t="str">
+        <x:v>Compara tasa de ganancia por subdirección</x:v>
+      </x:c>
+      <x:c r="C104" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} presenta una tasa de ganancia de {Valor1}% y {Entidad2} de {Valor2}%. La diferencia es {Diferencia} puntos porcentuales; {Lider} tiene la mayor rentabilidad esperada.</x:v>
+      </x:c>
+      <x:c r="D104" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="E104" s="28" t="str">
+        <x:v>Subdirección</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="58" customHeight="1">
+      <x:c r="A105" s="28" t="str">
+        <x:v>comparar_tasa_ganancia_zona</x:v>
+      </x:c>
+      <x:c r="B105" s="28" t="str">
+        <x:v>Compara tasa de ganancia por zona</x:v>
+      </x:c>
+      <x:c r="C105" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} presenta una tasa de ganancia de {Valor1}% y {Entidad2} de {Valor2}%. La diferencia es {Diferencia} puntos porcentuales; {Lider} tiene la mayor rentabilidad esperada.</x:v>
+      </x:c>
+      <x:c r="D105" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="E105" s="28" t="str">
+        <x:v>Zona</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="58" customHeight="1">
+      <x:c r="A106" s="28" t="str">
+        <x:v>comparar_tasa_ganancia_sucursal</x:v>
+      </x:c>
+      <x:c r="B106" s="28" t="str">
+        <x:v>Compara tasa de ganancia por sucursal</x:v>
+      </x:c>
+      <x:c r="C106" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} presenta una tasa de ganancia de {Valor1}% y {Entidad2} de {Valor2}%. La diferencia es {Diferencia} puntos porcentuales; {Lider} tiene la mayor rentabilidad esperada.</x:v>
+      </x:c>
+      <x:c r="D106" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="E106" s="28" t="str">
+        <x:v>Sucursal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="58" customHeight="1">
+      <x:c r="A107" s="28" t="str">
+        <x:v>comparar_tasa_ganancia_coordinacion</x:v>
+      </x:c>
+      <x:c r="B107" s="28" t="str">
+        <x:v>Compara tasa de ganancia por coordinación</x:v>
+      </x:c>
+      <x:c r="C107" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} presenta una tasa de ganancia de {Valor1}% y {Entidad2} de {Valor2}%. La diferencia es {Diferencia} puntos porcentuales; {Lider} tiene la mayor rentabilidad esperada.</x:v>
+      </x:c>
+      <x:c r="D107" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="E107" s="28" t="str">
+        <x:v>Coordinacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="58" customHeight="1">
+      <x:c r="A108" s="28" t="str">
+        <x:v>comparar_distribuidoras_corriente_estructura</x:v>
+      </x:c>
+      <x:c r="B108" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente entre toda la estructura</x:v>
+      </x:c>
+      <x:c r="C108" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras al corriente y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor base al corriente.</x:v>
+      </x:c>
+      <x:c r="D108" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="E108" s="28" t="str">
+        <x:v>Nivel detectado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="58" customHeight="1">
+      <x:c r="A109" s="28" t="str">
+        <x:v>comparar_distribuidoras_corriente_subdireccion</x:v>
+      </x:c>
+      <x:c r="B109" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente por subdirección</x:v>
+      </x:c>
+      <x:c r="C109" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras al corriente y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor base al corriente.</x:v>
+      </x:c>
+      <x:c r="D109" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="E109" s="28" t="str">
+        <x:v>Subdirección</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="58" customHeight="1">
+      <x:c r="A110" s="28" t="str">
+        <x:v>comparar_distribuidoras_corriente_zona</x:v>
+      </x:c>
+      <x:c r="B110" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente por zona</x:v>
+      </x:c>
+      <x:c r="C110" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras al corriente y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor base al corriente.</x:v>
+      </x:c>
+      <x:c r="D110" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="E110" s="28" t="str">
+        <x:v>Zona</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="58" customHeight="1">
+      <x:c r="A111" s="28" t="str">
+        <x:v>comparar_distribuidoras_corriente_sucursal</x:v>
+      </x:c>
+      <x:c r="B111" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente por sucursal</x:v>
+      </x:c>
+      <x:c r="C111" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras al corriente y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor base al corriente.</x:v>
+      </x:c>
+      <x:c r="D111" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="E111" s="28" t="str">
+        <x:v>Sucursal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="58" customHeight="1">
+      <x:c r="A112" s="28" t="str">
+        <x:v>comparar_distribuidoras_corriente_coordinacion</x:v>
+      </x:c>
+      <x:c r="B112" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente por coordinación</x:v>
+      </x:c>
+      <x:c r="C112" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras al corriente y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor base al corriente.</x:v>
+      </x:c>
+      <x:c r="D112" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="E112" s="28" t="str">
+        <x:v>Coordinacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="58" customHeight="1">
+      <x:c r="A113" s="28" t="str">
+        <x:v>comparar_distribuidoras_mora_estructura</x:v>
+      </x:c>
+      <x:c r="B113" s="28" t="str">
+        <x:v>Compara distribuidoras con mora entre toda la estructura</x:v>
+      </x:c>
+      <x:c r="C113" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras con mora y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor exposición en mora.</x:v>
+      </x:c>
+      <x:c r="D113" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="E113" s="28" t="str">
+        <x:v>Nivel detectado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="58" customHeight="1">
+      <x:c r="A114" s="28" t="str">
+        <x:v>comparar_distribuidoras_mora_subdireccion</x:v>
+      </x:c>
+      <x:c r="B114" s="28" t="str">
+        <x:v>Compara distribuidoras con mora por subdirección</x:v>
+      </x:c>
+      <x:c r="C114" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras con mora y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor exposición en mora.</x:v>
+      </x:c>
+      <x:c r="D114" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="E114" s="28" t="str">
+        <x:v>Subdirección</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="58" customHeight="1">
+      <x:c r="A115" s="28" t="str">
+        <x:v>comparar_distribuidoras_mora_zona</x:v>
+      </x:c>
+      <x:c r="B115" s="28" t="str">
+        <x:v>Compara distribuidoras con mora por zona</x:v>
+      </x:c>
+      <x:c r="C115" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras con mora y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor exposición en mora.</x:v>
+      </x:c>
+      <x:c r="D115" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="E115" s="28" t="str">
+        <x:v>Zona</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="58" customHeight="1">
+      <x:c r="A116" s="28" t="str">
+        <x:v>comparar_distribuidoras_mora_sucursal</x:v>
+      </x:c>
+      <x:c r="B116" s="28" t="str">
+        <x:v>Compara distribuidoras con mora por sucursal</x:v>
+      </x:c>
+      <x:c r="C116" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras con mora y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor exposición en mora.</x:v>
+      </x:c>
+      <x:c r="D116" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="E116" s="28" t="str">
+        <x:v>Sucursal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="58" customHeight="1">
+      <x:c r="A117" s="28" t="str">
+        <x:v>comparar_distribuidoras_mora_coordinacion</x:v>
+      </x:c>
+      <x:c r="B117" s="28" t="str">
+        <x:v>Compara distribuidoras con mora por coordinación</x:v>
+      </x:c>
+      <x:c r="C117" s="28" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras con mora y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor exposición en mora.</x:v>
+      </x:c>
+      <x:c r="D117" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="E117" s="28" t="str">
+        <x:v>Coordinacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="58" customHeight="1">
+      <x:c r="A118" s="28" t="str">
+        <x:v>comparar_dos_entidades_todas_variables</x:v>
+      </x:c>
+      <x:c r="B118" s="28" t="str">
+        <x:v>Compara Cd. Juárez con Tampico Centro en todas las variables</x:v>
+      </x:c>
+      <x:c r="C118" s="28" t="str">
+        <x:v>{Entidad1} vs {Entidad2}: canjes, dispersión, tasa, distribuidoras al corriente y con mora.</x:v>
+      </x:c>
+      <x:c r="D118" s="28" t="str">
+        <x:v>Distribuidoras MX + Dispersión diaria + Plazo y composición</x:v>
+      </x:c>
+      <x:c r="E118" s="28" t="str">
+        <x:v>Nivel detectado</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7b3ef4efd644ed5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7812a609068430f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9009,7 +10506,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R223c5281028b47fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6f52c38336d40f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9259,4 +10756,587 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="46" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="68" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="128" t="str">
+        <x:v>MATRIZ DE COMPARACIONES ENTRE TODA LA ESTRUCTURA</x:v>
+      </x:c>
+      <x:c r="B1" s="128"/>
+      <x:c r="C1" s="128"/>
+      <x:c r="D1" s="128"/>
+      <x:c r="E1" s="128"/>
+      <x:c r="F1" s="128"/>
+      <x:c r="G1" s="128"/>
+      <x:c r="H1" s="128"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="132" t="str">
+        <x:v>Nivel estructural</x:v>
+      </x:c>
+      <x:c r="B3" s="132" t="str">
+        <x:v>Variable</x:v>
+      </x:c>
+      <x:c r="C3" s="132" t="str">
+        <x:v>Base origen</x:v>
+      </x:c>
+      <x:c r="D3" s="132" t="str">
+        <x:v>Campo(s)</x:v>
+      </x:c>
+      <x:c r="E3" s="132" t="str">
+        <x:v>Cálculo</x:v>
+      </x:c>
+      <x:c r="F3" s="132" t="str">
+        <x:v>Orden recomendado</x:v>
+      </x:c>
+      <x:c r="G3" s="132" t="str">
+        <x:v>Pregunta ejemplo</x:v>
+      </x:c>
+      <x:c r="H3" s="132" t="str">
+        <x:v>Respuesta esperada</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="54" customHeight="1">
+      <x:c r="A4" s="123" t="str">
+        <x:v>Subdirección</x:v>
+      </x:c>
+      <x:c r="B4" s="28" t="str">
+        <x:v>Canjes</x:v>
+      </x:c>
+      <x:c r="C4" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D4" s="28" t="str">
+        <x:v>Canjes</x:v>
+      </x:c>
+      <x:c r="E4" s="124" t="str">
+        <x:v>SUM(Canjes)</x:v>
+      </x:c>
+      <x:c r="F4" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G4" s="28" t="str">
+        <x:v>Compara canjes por subdirección</x:v>
+      </x:c>
+      <x:c r="H4" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} registra {Valor1} canjes y {Entidad2} registra {Valor2}. La diferencia es {Diferencia} canjes y {Lider} presenta el mayor volumen.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="54" customHeight="1">
+      <x:c r="A5" s="123" t="str">
+        <x:v>Subdirección</x:v>
+      </x:c>
+      <x:c r="B5" s="28" t="str">
+        <x:v>Dispersión Acumulada</x:v>
+      </x:c>
+      <x:c r="C5" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D5" s="28" t="str">
+        <x:v>Total dispersado</x:v>
+      </x:c>
+      <x:c r="E5" s="124" t="str">
+        <x:v>SUM(Total dispersado)</x:v>
+      </x:c>
+      <x:c r="F5" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G5" s="28" t="str">
+        <x:v>Compara dispersión acumulada por subdirección</x:v>
+      </x:c>
+      <x:c r="H5" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} acumula {Valor1} de dispersión y {Entidad2} acumula {Valor2}. La diferencia es {Diferencia}; {Lider} concentra el mayor monto.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="54" customHeight="1">
+      <x:c r="A6" s="123" t="str">
+        <x:v>Subdirección</x:v>
+      </x:c>
+      <x:c r="B6" s="28" t="str">
+        <x:v>Tasa De Ganancia</x:v>
+      </x:c>
+      <x:c r="C6" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="D6" s="28" t="str">
+        <x:v>Interes; Capital</x:v>
+      </x:c>
+      <x:c r="E6" s="124" t="str">
+        <x:v>DIV(SUM(Interes),SUM(Capital))*100</x:v>
+      </x:c>
+      <x:c r="F6" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G6" s="28" t="str">
+        <x:v>Compara tasa de ganancia por subdirección</x:v>
+      </x:c>
+      <x:c r="H6" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} presenta una tasa de ganancia de {Valor1}% y {Entidad2} de {Valor2}%. La diferencia es {Diferencia} puntos porcentuales; {Lider} tiene la mayor rentabilidad esperada.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="54" customHeight="1">
+      <x:c r="A7" s="123" t="str">
+        <x:v>Subdirección</x:v>
+      </x:c>
+      <x:c r="B7" s="28" t="str">
+        <x:v>Distribuidoras Al Corriente</x:v>
+      </x:c>
+      <x:c r="C7" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D7" s="28" t="str">
+        <x:v>Distribuidoras al Corriente H</x:v>
+      </x:c>
+      <x:c r="E7" s="124" t="str">
+        <x:v>SUM(Distribuidoras al Corriente H)</x:v>
+      </x:c>
+      <x:c r="F7" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G7" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente por subdirección</x:v>
+      </x:c>
+      <x:c r="H7" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras al corriente y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor base al corriente.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="54" customHeight="1">
+      <x:c r="A8" s="123" t="str">
+        <x:v>Subdirección</x:v>
+      </x:c>
+      <x:c r="B8" s="28" t="str">
+        <x:v>Distribuidoras Con Mora</x:v>
+      </x:c>
+      <x:c r="C8" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D8" s="28" t="str">
+        <x:v>Distribuidoras en Mora H</x:v>
+      </x:c>
+      <x:c r="E8" s="124" t="str">
+        <x:v>SUM(Distribuidoras en Mora H)</x:v>
+      </x:c>
+      <x:c r="F8" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G8" s="28" t="str">
+        <x:v>Compara distribuidoras con mora por subdirección</x:v>
+      </x:c>
+      <x:c r="H8" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras con mora y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor exposición en mora.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="54" customHeight="1">
+      <x:c r="A9" s="123" t="str">
+        <x:v>Zona</x:v>
+      </x:c>
+      <x:c r="B9" s="28" t="str">
+        <x:v>Canjes</x:v>
+      </x:c>
+      <x:c r="C9" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D9" s="28" t="str">
+        <x:v>Canjes</x:v>
+      </x:c>
+      <x:c r="E9" s="124" t="str">
+        <x:v>SUM(Canjes)</x:v>
+      </x:c>
+      <x:c r="F9" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G9" s="28" t="str">
+        <x:v>Compara canjes por zona</x:v>
+      </x:c>
+      <x:c r="H9" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} registra {Valor1} canjes y {Entidad2} registra {Valor2}. La diferencia es {Diferencia} canjes y {Lider} presenta el mayor volumen.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="54" customHeight="1">
+      <x:c r="A10" s="123" t="str">
+        <x:v>Zona</x:v>
+      </x:c>
+      <x:c r="B10" s="28" t="str">
+        <x:v>Dispersión Acumulada</x:v>
+      </x:c>
+      <x:c r="C10" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="str">
+        <x:v>Total dispersado</x:v>
+      </x:c>
+      <x:c r="E10" s="124" t="str">
+        <x:v>SUM(Total dispersado)</x:v>
+      </x:c>
+      <x:c r="F10" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G10" s="28" t="str">
+        <x:v>Compara dispersión acumulada por zona</x:v>
+      </x:c>
+      <x:c r="H10" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} acumula {Valor1} de dispersión y {Entidad2} acumula {Valor2}. La diferencia es {Diferencia}; {Lider} concentra el mayor monto.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="54" customHeight="1">
+      <x:c r="A11" s="123" t="str">
+        <x:v>Zona</x:v>
+      </x:c>
+      <x:c r="B11" s="28" t="str">
+        <x:v>Tasa De Ganancia</x:v>
+      </x:c>
+      <x:c r="C11" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="str">
+        <x:v>Interes; Capital</x:v>
+      </x:c>
+      <x:c r="E11" s="124" t="str">
+        <x:v>DIV(SUM(Interes),SUM(Capital))*100</x:v>
+      </x:c>
+      <x:c r="F11" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G11" s="28" t="str">
+        <x:v>Compara tasa de ganancia por zona</x:v>
+      </x:c>
+      <x:c r="H11" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} presenta una tasa de ganancia de {Valor1}% y {Entidad2} de {Valor2}%. La diferencia es {Diferencia} puntos porcentuales; {Lider} tiene la mayor rentabilidad esperada.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="54" customHeight="1">
+      <x:c r="A12" s="123" t="str">
+        <x:v>Zona</x:v>
+      </x:c>
+      <x:c r="B12" s="28" t="str">
+        <x:v>Distribuidoras Al Corriente</x:v>
+      </x:c>
+      <x:c r="C12" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="str">
+        <x:v>Distribuidoras al Corriente H</x:v>
+      </x:c>
+      <x:c r="E12" s="124" t="str">
+        <x:v>SUM(Distribuidoras al Corriente H)</x:v>
+      </x:c>
+      <x:c r="F12" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G12" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente por zona</x:v>
+      </x:c>
+      <x:c r="H12" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras al corriente y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor base al corriente.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="54" customHeight="1">
+      <x:c r="A13" s="123" t="str">
+        <x:v>Zona</x:v>
+      </x:c>
+      <x:c r="B13" s="28" t="str">
+        <x:v>Distribuidoras Con Mora</x:v>
+      </x:c>
+      <x:c r="C13" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D13" s="28" t="str">
+        <x:v>Distribuidoras en Mora H</x:v>
+      </x:c>
+      <x:c r="E13" s="124" t="str">
+        <x:v>SUM(Distribuidoras en Mora H)</x:v>
+      </x:c>
+      <x:c r="F13" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G13" s="28" t="str">
+        <x:v>Compara distribuidoras con mora por zona</x:v>
+      </x:c>
+      <x:c r="H13" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras con mora y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor exposición en mora.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="54" customHeight="1">
+      <x:c r="A14" s="123" t="str">
+        <x:v>Sucursal</x:v>
+      </x:c>
+      <x:c r="B14" s="28" t="str">
+        <x:v>Canjes</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D14" s="28" t="str">
+        <x:v>Canjes</x:v>
+      </x:c>
+      <x:c r="E14" s="124" t="str">
+        <x:v>SUM(Canjes)</x:v>
+      </x:c>
+      <x:c r="F14" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G14" s="28" t="str">
+        <x:v>Compara canjes por sucursal</x:v>
+      </x:c>
+      <x:c r="H14" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} registra {Valor1} canjes y {Entidad2} registra {Valor2}. La diferencia es {Diferencia} canjes y {Lider} presenta el mayor volumen.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="54" customHeight="1">
+      <x:c r="A15" s="123" t="str">
+        <x:v>Sucursal</x:v>
+      </x:c>
+      <x:c r="B15" s="28" t="str">
+        <x:v>Dispersión Acumulada</x:v>
+      </x:c>
+      <x:c r="C15" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D15" s="28" t="str">
+        <x:v>Total dispersado</x:v>
+      </x:c>
+      <x:c r="E15" s="124" t="str">
+        <x:v>SUM(Total dispersado)</x:v>
+      </x:c>
+      <x:c r="F15" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G15" s="28" t="str">
+        <x:v>Compara dispersión acumulada por sucursal</x:v>
+      </x:c>
+      <x:c r="H15" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} acumula {Valor1} de dispersión y {Entidad2} acumula {Valor2}. La diferencia es {Diferencia}; {Lider} concentra el mayor monto.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="54" customHeight="1">
+      <x:c r="A16" s="123" t="str">
+        <x:v>Sucursal</x:v>
+      </x:c>
+      <x:c r="B16" s="28" t="str">
+        <x:v>Tasa De Ganancia</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="D16" s="28" t="str">
+        <x:v>Interes; Capital</x:v>
+      </x:c>
+      <x:c r="E16" s="124" t="str">
+        <x:v>DIV(SUM(Interes),SUM(Capital))*100</x:v>
+      </x:c>
+      <x:c r="F16" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G16" s="28" t="str">
+        <x:v>Compara tasa de ganancia por sucursal</x:v>
+      </x:c>
+      <x:c r="H16" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} presenta una tasa de ganancia de {Valor1}% y {Entidad2} de {Valor2}%. La diferencia es {Diferencia} puntos porcentuales; {Lider} tiene la mayor rentabilidad esperada.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="54" customHeight="1">
+      <x:c r="A17" s="123" t="str">
+        <x:v>Sucursal</x:v>
+      </x:c>
+      <x:c r="B17" s="28" t="str">
+        <x:v>Distribuidoras Al Corriente</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D17" s="28" t="str">
+        <x:v>Distribuidoras al Corriente H</x:v>
+      </x:c>
+      <x:c r="E17" s="124" t="str">
+        <x:v>SUM(Distribuidoras al Corriente H)</x:v>
+      </x:c>
+      <x:c r="F17" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G17" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente por sucursal</x:v>
+      </x:c>
+      <x:c r="H17" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras al corriente y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor base al corriente.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="54" customHeight="1">
+      <x:c r="A18" s="123" t="str">
+        <x:v>Sucursal</x:v>
+      </x:c>
+      <x:c r="B18" s="28" t="str">
+        <x:v>Distribuidoras Con Mora</x:v>
+      </x:c>
+      <x:c r="C18" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D18" s="28" t="str">
+        <x:v>Distribuidoras en Mora H</x:v>
+      </x:c>
+      <x:c r="E18" s="124" t="str">
+        <x:v>SUM(Distribuidoras en Mora H)</x:v>
+      </x:c>
+      <x:c r="F18" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G18" s="28" t="str">
+        <x:v>Compara distribuidoras con mora por sucursal</x:v>
+      </x:c>
+      <x:c r="H18" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras con mora y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor exposición en mora.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="54" customHeight="1">
+      <x:c r="A19" s="123" t="str">
+        <x:v>Coordinacion</x:v>
+      </x:c>
+      <x:c r="B19" s="28" t="str">
+        <x:v>Canjes</x:v>
+      </x:c>
+      <x:c r="C19" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D19" s="28" t="str">
+        <x:v>Canjes</x:v>
+      </x:c>
+      <x:c r="E19" s="124" t="str">
+        <x:v>SUM(Canjes)</x:v>
+      </x:c>
+      <x:c r="F19" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G19" s="28" t="str">
+        <x:v>Compara canjes por coordinación</x:v>
+      </x:c>
+      <x:c r="H19" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} registra {Valor1} canjes y {Entidad2} registra {Valor2}. La diferencia es {Diferencia} canjes y {Lider} presenta el mayor volumen.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="54" customHeight="1">
+      <x:c r="A20" s="123" t="str">
+        <x:v>Coordinacion</x:v>
+      </x:c>
+      <x:c r="B20" s="28" t="str">
+        <x:v>Dispersión Acumulada</x:v>
+      </x:c>
+      <x:c r="C20" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D20" s="28" t="str">
+        <x:v>Total dispersado</x:v>
+      </x:c>
+      <x:c r="E20" s="124" t="str">
+        <x:v>SUM(Total dispersado)</x:v>
+      </x:c>
+      <x:c r="F20" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G20" s="28" t="str">
+        <x:v>Compara dispersión acumulada por coordinación</x:v>
+      </x:c>
+      <x:c r="H20" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} acumula {Valor1} de dispersión y {Entidad2} acumula {Valor2}. La diferencia es {Diferencia}; {Lider} concentra el mayor monto.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="54" customHeight="1">
+      <x:c r="A21" s="123" t="str">
+        <x:v>Coordinacion</x:v>
+      </x:c>
+      <x:c r="B21" s="28" t="str">
+        <x:v>Tasa De Ganancia</x:v>
+      </x:c>
+      <x:c r="C21" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="D21" s="28" t="str">
+        <x:v>Interes; Capital</x:v>
+      </x:c>
+      <x:c r="E21" s="124" t="str">
+        <x:v>DIV(SUM(Interes),SUM(Capital))*100</x:v>
+      </x:c>
+      <x:c r="F21" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G21" s="28" t="str">
+        <x:v>Compara tasa de ganancia por coordinación</x:v>
+      </x:c>
+      <x:c r="H21" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} presenta una tasa de ganancia de {Valor1}% y {Entidad2} de {Valor2}%. La diferencia es {Diferencia} puntos porcentuales; {Lider} tiene la mayor rentabilidad esperada.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="54" customHeight="1">
+      <x:c r="A22" s="123" t="str">
+        <x:v>Coordinacion</x:v>
+      </x:c>
+      <x:c r="B22" s="28" t="str">
+        <x:v>Distribuidoras Al Corriente</x:v>
+      </x:c>
+      <x:c r="C22" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D22" s="28" t="str">
+        <x:v>Distribuidoras al Corriente H</x:v>
+      </x:c>
+      <x:c r="E22" s="124" t="str">
+        <x:v>SUM(Distribuidoras al Corriente H)</x:v>
+      </x:c>
+      <x:c r="F22" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G22" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente por coordinación</x:v>
+      </x:c>
+      <x:c r="H22" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras al corriente y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor base al corriente.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="54" customHeight="1">
+      <x:c r="A23" s="123" t="str">
+        <x:v>Coordinacion</x:v>
+      </x:c>
+      <x:c r="B23" s="28" t="str">
+        <x:v>Distribuidoras Con Mora</x:v>
+      </x:c>
+      <x:c r="C23" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D23" s="28" t="str">
+        <x:v>Distribuidoras en Mora H</x:v>
+      </x:c>
+      <x:c r="E23" s="124" t="str">
+        <x:v>SUM(Distribuidoras en Mora H)</x:v>
+      </x:c>
+      <x:c r="F23" s="28" t="str">
+        <x:v>DESC para ranking / comparación directa entre dos entidades</x:v>
+      </x:c>
+      <x:c r="G23" s="28" t="str">
+        <x:v>Compara distribuidoras con mora por coordinación</x:v>
+      </x:c>
+      <x:c r="H23" s="125" t="str">
+        <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras con mora y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor exposición en mora.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9dc5d5fb55564510"/>
+  </x:tableParts>
+</x:worksheet>
 </file>
--- a/Catalogo_completo_reglas_chatbot_valeras.xlsx
+++ b/Catalogo_completo_reglas_chatbot_valeras.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reglas Chatbot" sheetId="1" r:id="R3337a7c4fd514ad8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo Métricas" sheetId="2" r:id="R7c4be78051fc40d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diccionario Columnas" sheetId="3" r:id="R8f238c45d870462a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categorías Bonificaciones" sheetId="4" r:id="Rb082cec98b274995"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preguntas Ejemplo" sheetId="5" r:id="R214cd387f5bf458f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sintaxis Fórmulas" sheetId="6" r:id="R90e8b8e8aa8e42df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guía Implementación" sheetId="7" r:id="R7ba6a85595924309"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz Comparaciones" sheetId="8" r:id="R570f57a0685947c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reglas Chatbot" sheetId="1" r:id="Rb7db3aab65fa4f9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo Métricas" sheetId="2" r:id="R99419cc24084483a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diccionario Columnas" sheetId="3" r:id="R620b388683fb468c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categorías Bonificaciones" sheetId="4" r:id="R9153df8f9d2e48e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preguntas Ejemplo" sheetId="5" r:id="R25d7a9d02fcf4d37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sintaxis Fórmulas" sheetId="6" r:id="R71f7be15bf174015"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guía Implementación" sheetId="7" r:id="R8301d11dae1844ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz Comparaciones" sheetId="8" r:id="R15089c28fac345bc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -49,7 +49,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="12">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -106,6 +106,21 @@
         <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="24">
     <x:border/>
@@ -136,7 +151,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="133">
+  <x:cellXfs count="137">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -501,6 +516,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -532,7 +559,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReglasChatbotTable" displayName="ReglasChatbotTable" ref="A3:L118" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReglasChatbotTable" displayName="ReglasChatbotTable" ref="A3:L124" headerRowCount="1">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="Intención"/>
     <x:tableColumn id="2" name="Palabras clave"/>
@@ -581,7 +608,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PreguntasTable" displayName="PreguntasTable" ref="A3:E118" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PreguntasTable" displayName="PreguntasTable" ref="A3:E124" headerRowCount="1">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Intención"/>
     <x:tableColumn id="2" name="Pregunta ejemplo"/>
@@ -608,7 +635,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="MatrizComparacionesTable" displayName="MatrizComparacionesTable" ref="A3:H23" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="MatrizComparacionesTable" displayName="MatrizComparacionesTable" ref="A3:H28" headerRowCount="1">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Nivel estructural"/>
     <x:tableColumn id="2" name="Variable"/>
@@ -5210,6 +5237,234 @@
         <x:v>La conclusión debe identificar fortalezas y riesgos sin mezclar escalas. La tasa de ganancia es ponderada.</x:v>
       </x:c>
     </x:row>
+    <x:row r="119" ht="64" customHeight="1">
+      <x:c r="A119" s="134" t="str">
+        <x:v>comparar_tasa_ganancia_top_bottom</x:v>
+      </x:c>
+      <x:c r="B119" s="28" t="str">
+        <x:v>compara tasa de ganancia top y bottom, top 5 y bottom 5 tasa de ganancia, mejores y peores tasas, ranking superior e inferior de rentabilidad</x:v>
+      </x:c>
+      <x:c r="C119" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="D119" s="28" t="str">
+        <x:v>Interes; Capital; Subdirección; Zona; Sucursal; Coordinacion</x:v>
+      </x:c>
+      <x:c r="E119" s="135" t="str">
+        <x:v>TOP_BOTTOM(N,DIV(SUM(Interes),SUM(Capital))*100)</x:v>
+      </x:c>
+      <x:c r="F119" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+      <x:c r="G119" s="28" t="str">
+        <x:v>Marca activa; mismo corte; Capital &gt; 0; filtros activos; excluir Sin dato</x:v>
+      </x:c>
+      <x:c r="H119" s="28" t="str">
+        <x:v>DESC para Top N y ASC para Bottom N</x:v>
+      </x:c>
+      <x:c r="I119" s="28" t="str">
+        <x:v>Dos listas con porcentaje</x:v>
+      </x:c>
+      <x:c r="J119" s="136" t="str">
+        <x:v>Top {N}: {ListaTop}. Bottom {N}: {ListaBottom}. La diferencia entre el líder y el último es {Diferencia} puntos porcentuales.</x:v>
+      </x:c>
+      <x:c r="K119" s="28" t="str">
+        <x:v>Compara la tasa de ganancia top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="L119" s="28" t="str">
+        <x:v>Detectar N en la pregunta; si sólo aparece una vez, usar el mismo valor para Top y Bottom. Por defecto N=5.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="64" customHeight="1">
+      <x:c r="A120" s="134" t="str">
+        <x:v>comparar_canjes_top_bottom</x:v>
+      </x:c>
+      <x:c r="B120" s="28" t="str">
+        <x:v>compara canjes top y bottom, top 5 y bottom 5 canjes, mayores y menores canjes, ranking superior e inferior de canjes</x:v>
+      </x:c>
+      <x:c r="C120" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D120" s="28" t="str">
+        <x:v>Canjes; Subdirección; Zona; Sucursal; Coordinacion</x:v>
+      </x:c>
+      <x:c r="E120" s="135" t="str">
+        <x:v>TOP_BOTTOM(N,SUM(Canjes))</x:v>
+      </x:c>
+      <x:c r="F120" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+      <x:c r="G120" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros activos; excluir Sin dato</x:v>
+      </x:c>
+      <x:c r="H120" s="28" t="str">
+        <x:v>DESC para Top N y ASC para Bottom N</x:v>
+      </x:c>
+      <x:c r="I120" s="28" t="str">
+        <x:v>Dos listas con número</x:v>
+      </x:c>
+      <x:c r="J120" s="136" t="str">
+        <x:v>Top {N} en canjes: {ListaTop}. Bottom {N} en canjes: {ListaBottom}.</x:v>
+      </x:c>
+      <x:c r="K120" s="28" t="str">
+        <x:v>Compara los canjes top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="L120" s="28" t="str">
+        <x:v>Detectar N; por defecto 5. Excluir entidades sin operación cuando se solicite actividad efectiva.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="64" customHeight="1">
+      <x:c r="A121" s="134" t="str">
+        <x:v>comparar_dispersion_top_bottom</x:v>
+      </x:c>
+      <x:c r="B121" s="28" t="str">
+        <x:v>compara dispersión top y bottom, top 5 y bottom 5 dispersión, mayor y menor dispersado, ranking superior e inferior de dispersión</x:v>
+      </x:c>
+      <x:c r="C121" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D121" s="28" t="str">
+        <x:v>Total dispersado; Subdirección; Zona; Sucursal; Coordinacion</x:v>
+      </x:c>
+      <x:c r="E121" s="135" t="str">
+        <x:v>TOP_BOTTOM(N,SUM(Total dispersado))</x:v>
+      </x:c>
+      <x:c r="F121" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+      <x:c r="G121" s="28" t="str">
+        <x:v>Marca activa; fecha &lt;= corte; filtros activos; excluir Sin dato</x:v>
+      </x:c>
+      <x:c r="H121" s="28" t="str">
+        <x:v>DESC para Top N y ASC para Bottom N</x:v>
+      </x:c>
+      <x:c r="I121" s="28" t="str">
+        <x:v>Dos listas con moneda</x:v>
+      </x:c>
+      <x:c r="J121" s="136" t="str">
+        <x:v>Top {N} en dispersión: {ListaTop}. Bottom {N} en dispersión: {ListaBottom}.</x:v>
+      </x:c>
+      <x:c r="K121" s="28" t="str">
+        <x:v>Compara la dispersión top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="L121" s="28" t="str">
+        <x:v>Detectar N; por defecto 5. Distinguir acumulado de dato del día.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="64" customHeight="1">
+      <x:c r="A122" s="134" t="str">
+        <x:v>comparar_corriente_top_bottom</x:v>
+      </x:c>
+      <x:c r="B122" s="28" t="str">
+        <x:v>compara distribuidoras al corriente top y bottom, top 5 y bottom 5 al corriente, mayores y menores distribuidoras al corriente</x:v>
+      </x:c>
+      <x:c r="C122" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D122" s="28" t="str">
+        <x:v>Distribuidoras al Corriente H; Subdirección; Zona; Sucursal; Coordinacion</x:v>
+      </x:c>
+      <x:c r="E122" s="135" t="str">
+        <x:v>TOP_BOTTOM(N,SUM(Distribuidoras al Corriente H))</x:v>
+      </x:c>
+      <x:c r="F122" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+      <x:c r="G122" s="28" t="str">
+        <x:v>Marca activa; último corte; filtros activos; excluir Sin dato</x:v>
+      </x:c>
+      <x:c r="H122" s="28" t="str">
+        <x:v>DESC para Top N y ASC para Bottom N</x:v>
+      </x:c>
+      <x:c r="I122" s="28" t="str">
+        <x:v>Dos listas con número</x:v>
+      </x:c>
+      <x:c r="J122" s="136" t="str">
+        <x:v>Top {N} en distribuidoras al corriente: {ListaTop}. Bottom {N}: {ListaBottom}.</x:v>
+      </x:c>
+      <x:c r="K122" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="L122" s="28" t="str">
+        <x:v>Detectar N; por defecto 5. No confundir cantidad con porcentaje.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="64" customHeight="1">
+      <x:c r="A123" s="134" t="str">
+        <x:v>comparar_mora_top_bottom</x:v>
+      </x:c>
+      <x:c r="B123" s="28" t="str">
+        <x:v>compara distribuidoras con mora top y bottom, top 5 y bottom 5 mora, mayores y menores distribuidoras en mora</x:v>
+      </x:c>
+      <x:c r="C123" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D123" s="28" t="str">
+        <x:v>Distribuidoras en Mora H; Subdirección; Zona; Sucursal; Coordinacion</x:v>
+      </x:c>
+      <x:c r="E123" s="135" t="str">
+        <x:v>TOP_BOTTOM(N,SUM(Distribuidoras en Mora H))</x:v>
+      </x:c>
+      <x:c r="F123" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+      <x:c r="G123" s="28" t="str">
+        <x:v>Marca activa; último corte; filtros activos; excluir Sin dato</x:v>
+      </x:c>
+      <x:c r="H123" s="28" t="str">
+        <x:v>DESC para Top N y ASC para Bottom N</x:v>
+      </x:c>
+      <x:c r="I123" s="28" t="str">
+        <x:v>Dos listas con número</x:v>
+      </x:c>
+      <x:c r="J123" s="136" t="str">
+        <x:v>Top {N} en distribuidoras con mora: {ListaTop}. Bottom {N}: {ListaBottom}.</x:v>
+      </x:c>
+      <x:c r="K123" s="28" t="str">
+        <x:v>Compara distribuidoras con mora top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="L123" s="28" t="str">
+        <x:v>Detectar N; por defecto 5. El Top representa mayor exposición; el Bottom menor exposición.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="64" customHeight="1">
+      <x:c r="A124" s="134" t="str">
+        <x:v>comparar_todas_variables_top_bottom</x:v>
+      </x:c>
+      <x:c r="B124" s="28" t="str">
+        <x:v>compara todas las variables top y bottom, top 5 y bottom 5 de toda la estructura, ranking completo superior e inferior</x:v>
+      </x:c>
+      <x:c r="C124" s="28" t="str">
+        <x:v>Distribuidoras MX + Dispersión diaria + Plazo y composición</x:v>
+      </x:c>
+      <x:c r="D124" s="28" t="str">
+        <x:v>Canjes; Total dispersado; Interes; Capital; Distribuidoras al Corriente H; Distribuidoras en Mora H</x:v>
+      </x:c>
+      <x:c r="E124" s="135" t="str">
+        <x:v>TOP_BOTTOM_ALL(N,[Canjes,Total dispersado,DIV(SUM(Interes),SUM(Capital))*100,Distribuidoras al Corriente H,Distribuidoras en Mora H])</x:v>
+      </x:c>
+      <x:c r="F124" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+      <x:c r="G124" s="28" t="str">
+        <x:v>Marca activa; mismo corte; filtros activos; excluir Sin dato</x:v>
+      </x:c>
+      <x:c r="H124" s="28" t="str">
+        <x:v>DESC y ASC por cada variable</x:v>
+      </x:c>
+      <x:c r="I124" s="28" t="str">
+        <x:v>Cinco bloques comparativos</x:v>
+      </x:c>
+      <x:c r="J124" s="136" t="str">
+        <x:v>Se presentan Top {N} y Bottom {N} para canjes, dispersión, tasa de ganancia, distribuidoras al corriente y distribuidoras con mora.</x:v>
+      </x:c>
+      <x:c r="K124" s="28" t="str">
+        <x:v>Compara todas las variables top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="L124" s="28" t="str">
+        <x:v>Generar una sección por variable. La tasa de ganancia debe calcularse ponderada.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:L1"/>
@@ -5229,7 +5484,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf56be3e57d6942b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R650250f75fd74a8f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6023,7 +6278,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a3d74b9ffd84475"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ed74a40893242a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7616,7 +7871,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0de2200e373c455b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd54b48a9c704ac9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10147,13 +10402,115 @@
         <x:v>Nivel detectado</x:v>
       </x:c>
     </x:row>
+    <x:row r="119" ht="58" customHeight="1">
+      <x:c r="A119" s="28" t="str">
+        <x:v>comparar_tasa_ganancia_top_bottom</x:v>
+      </x:c>
+      <x:c r="B119" s="28" t="str">
+        <x:v>Compara la tasa de ganancia top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="C119" s="28" t="str">
+        <x:v>Top {N}: {ListaTop}. Bottom {N}: {ListaBottom}. La diferencia entre el líder y el último es {Diferencia} puntos porcentuales.</x:v>
+      </x:c>
+      <x:c r="D119" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="E119" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="58" customHeight="1">
+      <x:c r="A120" s="28" t="str">
+        <x:v>comparar_canjes_top_bottom</x:v>
+      </x:c>
+      <x:c r="B120" s="28" t="str">
+        <x:v>Compara los canjes top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="C120" s="28" t="str">
+        <x:v>Top {N} en canjes: {ListaTop}. Bottom {N} en canjes: {ListaBottom}.</x:v>
+      </x:c>
+      <x:c r="D120" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="E120" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="58" customHeight="1">
+      <x:c r="A121" s="28" t="str">
+        <x:v>comparar_dispersion_top_bottom</x:v>
+      </x:c>
+      <x:c r="B121" s="28" t="str">
+        <x:v>Compara la dispersión top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="C121" s="28" t="str">
+        <x:v>Top {N} en dispersión: {ListaTop}. Bottom {N} en dispersión: {ListaBottom}.</x:v>
+      </x:c>
+      <x:c r="D121" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="E121" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="58" customHeight="1">
+      <x:c r="A122" s="28" t="str">
+        <x:v>comparar_corriente_top_bottom</x:v>
+      </x:c>
+      <x:c r="B122" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="C122" s="28" t="str">
+        <x:v>Top {N} en distribuidoras al corriente: {ListaTop}. Bottom {N}: {ListaBottom}.</x:v>
+      </x:c>
+      <x:c r="D122" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="E122" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="58" customHeight="1">
+      <x:c r="A123" s="28" t="str">
+        <x:v>comparar_mora_top_bottom</x:v>
+      </x:c>
+      <x:c r="B123" s="28" t="str">
+        <x:v>Compara distribuidoras con mora top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="C123" s="28" t="str">
+        <x:v>Top {N} en distribuidoras con mora: {ListaTop}. Bottom {N}: {ListaBottom}.</x:v>
+      </x:c>
+      <x:c r="D123" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="E123" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="58" customHeight="1">
+      <x:c r="A124" s="28" t="str">
+        <x:v>comparar_todas_variables_top_bottom</x:v>
+      </x:c>
+      <x:c r="B124" s="28" t="str">
+        <x:v>Compara todas las variables top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="C124" s="28" t="str">
+        <x:v>Se presentan Top {N} y Bottom {N} para canjes, dispersión, tasa de ganancia, distribuidoras al corriente y distribuidoras con mora.</x:v>
+      </x:c>
+      <x:c r="D124" s="28" t="str">
+        <x:v>Distribuidoras MX + Dispersión diaria + Plazo y composición</x:v>
+      </x:c>
+      <x:c r="E124" s="28" t="str">
+        <x:v>Nivel detectado: Subdirección / Zona / Sucursal / Coordinacion</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7812a609068430f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85aaf715b2874659"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10506,7 +10863,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6f52c38336d40f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re56891ce6eb44d3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11330,13 +11687,143 @@
         <x:v>Comparación de {Nivel}: {Entidad1} tiene {Valor1} distribuidoras con mora y {Entidad2} tiene {Valor2}. La diferencia es {Diferencia}; {Lider} concentra la mayor exposición en mora.</x:v>
       </x:c>
     </x:row>
+    <x:row r="24" ht="58" customHeight="1">
+      <x:c r="A24" s="134" t="str">
+        <x:v>Nivel detectado</x:v>
+      </x:c>
+      <x:c r="B24" s="28" t="str">
+        <x:v>Tasa de ganancia · Top/Bottom</x:v>
+      </x:c>
+      <x:c r="C24" s="28" t="str">
+        <x:v>Plazo y composición</x:v>
+      </x:c>
+      <x:c r="D24" s="28" t="str">
+        <x:v>Interes; Capital</x:v>
+      </x:c>
+      <x:c r="E24" s="135" t="str">
+        <x:v>TOP_BOTTOM(N,DIV(SUM(Interes),SUM(Capital))*100)</x:v>
+      </x:c>
+      <x:c r="F24" s="28" t="str">
+        <x:v>DESC Top / ASC Bottom</x:v>
+      </x:c>
+      <x:c r="G24" s="28" t="str">
+        <x:v>Compara tasa de ganancia top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="H24" s="136" t="str">
+        <x:v>Devuelve dos rankings con porcentaje y diferencia en puntos porcentuales.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="58" customHeight="1">
+      <x:c r="A25" s="134" t="str">
+        <x:v>Nivel detectado</x:v>
+      </x:c>
+      <x:c r="B25" s="28" t="str">
+        <x:v>Canjes · Top/Bottom</x:v>
+      </x:c>
+      <x:c r="C25" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D25" s="28" t="str">
+        <x:v>Canjes</x:v>
+      </x:c>
+      <x:c r="E25" s="135" t="str">
+        <x:v>TOP_BOTTOM(N,SUM(Canjes))</x:v>
+      </x:c>
+      <x:c r="F25" s="28" t="str">
+        <x:v>DESC Top / ASC Bottom</x:v>
+      </x:c>
+      <x:c r="G25" s="28" t="str">
+        <x:v>Compara canjes top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="H25" s="136" t="str">
+        <x:v>Devuelve dos rankings con número de canjes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="58" customHeight="1">
+      <x:c r="A26" s="134" t="str">
+        <x:v>Nivel detectado</x:v>
+      </x:c>
+      <x:c r="B26" s="28" t="str">
+        <x:v>Dispersión · Top/Bottom</x:v>
+      </x:c>
+      <x:c r="C26" s="28" t="str">
+        <x:v>Dispersión diaria</x:v>
+      </x:c>
+      <x:c r="D26" s="28" t="str">
+        <x:v>Total dispersado</x:v>
+      </x:c>
+      <x:c r="E26" s="135" t="str">
+        <x:v>TOP_BOTTOM(N,SUM(Total dispersado))</x:v>
+      </x:c>
+      <x:c r="F26" s="28" t="str">
+        <x:v>DESC Top / ASC Bottom</x:v>
+      </x:c>
+      <x:c r="G26" s="28" t="str">
+        <x:v>Compara dispersión top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="H26" s="136" t="str">
+        <x:v>Devuelve dos rankings con formato moneda.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="58" customHeight="1">
+      <x:c r="A27" s="134" t="str">
+        <x:v>Nivel detectado</x:v>
+      </x:c>
+      <x:c r="B27" s="28" t="str">
+        <x:v>Distribuidoras al corriente · Top/Bottom</x:v>
+      </x:c>
+      <x:c r="C27" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D27" s="28" t="str">
+        <x:v>Distribuidoras al Corriente H</x:v>
+      </x:c>
+      <x:c r="E27" s="135" t="str">
+        <x:v>TOP_BOTTOM(N,SUM(Distribuidoras al Corriente H))</x:v>
+      </x:c>
+      <x:c r="F27" s="28" t="str">
+        <x:v>DESC Top / ASC Bottom</x:v>
+      </x:c>
+      <x:c r="G27" s="28" t="str">
+        <x:v>Compara distribuidoras al corriente top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="H27" s="136" t="str">
+        <x:v>Devuelve dos rankings por cantidad.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="58" customHeight="1">
+      <x:c r="A28" s="134" t="str">
+        <x:v>Nivel detectado</x:v>
+      </x:c>
+      <x:c r="B28" s="28" t="str">
+        <x:v>Distribuidoras con mora · Top/Bottom</x:v>
+      </x:c>
+      <x:c r="C28" s="28" t="str">
+        <x:v>Distribuidoras MX</x:v>
+      </x:c>
+      <x:c r="D28" s="28" t="str">
+        <x:v>Distribuidoras en Mora H</x:v>
+      </x:c>
+      <x:c r="E28" s="135" t="str">
+        <x:v>TOP_BOTTOM(N,SUM(Distribuidoras en Mora H))</x:v>
+      </x:c>
+      <x:c r="F28" s="28" t="str">
+        <x:v>DESC Top / ASC Bottom</x:v>
+      </x:c>
+      <x:c r="G28" s="28" t="str">
+        <x:v>Compara distribuidoras con mora top 5 y bottom 5</x:v>
+      </x:c>
+      <x:c r="H28" s="136" t="str">
+        <x:v>Devuelve dos rankings; Top = mayor exposición.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9dc5d5fb55564510"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8c65df5eb144d6c"/>
   </x:tableParts>
 </x:worksheet>
 </file>